--- a/Input/urbs_intertemporal_2050/2049.xlsx
+++ b/Input/urbs_intertemporal_2050/2049.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29083378-434B-4A77-B474-7E860F2180C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B98EF8-B302-4476-BA22-B9E5BD8CA34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -175,9 +175,6 @@
     <t>Coal Plant</t>
   </si>
   <si>
-    <t>Coal Lignite</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT)</t>
   </si>
   <si>
@@ -313,31 +310,39 @@
     <t>EU27.Gas plant</t>
   </si>
   <si>
-    <t>Coal CCUS</t>
-  </si>
-  <si>
-    <t>Coal Lignite CCUS</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT) CCUS</t>
   </si>
   <si>
-    <t>Piped Gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LNG </t>
-  </si>
-  <si>
-    <t>Gas Plant (CCGT) LNG</t>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Slack</t>
+  </si>
+  <si>
+    <t>Lignite Plant</t>
+  </si>
+  <si>
+    <t>Other non-res</t>
+  </si>
+  <si>
+    <t>Oil Plant</t>
+  </si>
+  <si>
+    <t>Coal Plant CCUS</t>
+  </si>
+  <si>
+    <t>Lignite Plant CCUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -370,7 +375,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +442,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -483,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -519,7 +530,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -536,9 +546,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -550,11 +557,512 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="56">
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <top style="thin">
@@ -948,10 +1456,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1070,13 +1578,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1599,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1133,8 +1641,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="13" customWidth="1"/>
+    <col min="4" max="5" width="10.6640625" style="30" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="13"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1146,13 +1662,13 @@
       <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1166,15 +1682,15 @@
       <c r="C2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="22" t="e">
+      <c r="D2" s="21" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="E2" s="22" t="e">
+      <c r="E2" s="21" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="F2" s="22" t="e">
+      <c r="F2" s="21" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
@@ -1189,15 +1705,15 @@
       <c r="C3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="22" t="e">
+      <c r="D3" s="21" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="E3" s="22" t="e">
+      <c r="E3" s="21" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="F3" s="22" t="e">
+      <c r="F3" s="21" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
@@ -1215,10 +1731,10 @@
       <c r="D4">
         <v>8.64</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1227,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>21</v>
@@ -1235,10 +1751,10 @@
       <c r="D5">
         <v>20.52</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1255,10 +1771,10 @@
       <c r="D6">
         <v>147</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="25" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1275,10 +1791,10 @@
       <c r="D7">
         <v>64.8</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1295,10 +1811,10 @@
       <c r="D8">
         <v>6.12</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1315,10 +1831,10 @@
       <c r="D9">
         <v>6.48</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1327,31 +1843,54 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>21</v>
       </c>
       <c r="D10">
-        <v>36.54</v>
-      </c>
-      <c r="E10" s="27" t="s">
+        <v>32.04</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="26" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>32.04</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:B10">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="B8:B11">
+    <cfRule type="expression" dxfId="50" priority="1">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B11">
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Commodity price (€/MWh)" prompt="Cost for purchasing one unit (MWh) of a stock or buy commodity. Revenue for selling one unit (MWh) of a sell commodity. Cost for creating one unit of environmental commodity._x000a__x000a_Multiplier for sheet &quot;Buy-Sell-Price&quot; for commodity types &quot;Buy&quot; and &quot;Sell&quot;._x000a_" sqref="D1" xr:uid="{1264137D-8AF0-49FE-B965-C36086B11BA1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum commodity use" prompt="For stock commodities, this value limits annual use (MWh) of this commodity. For CO2, this value limits the amount of emissions (t_CO2). If simulation timespan does not cover a full year, the sums are multiplied accordingly before (cf. 'weight' in urbs)." sqref="E1" xr:uid="{9D124A69-88BC-40AC-84C5-653EFF19B24F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum commodity use per hour" prompt="For stock commodities, this value limits the energy use per hour (MW)._x000a_" sqref="F1" xr:uid="{80758E9F-7FFE-4068-951A-B2C06A5D58F3}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Commodity price (€/MWh)" prompt="Cost for purchasing one unit (MWh) of a stock or buy commodity. Revenue for selling one unit (MWh) of a sell commodity. Cost for creating one unit of environmental commodity._x000a__x000a_Multiplier for sheet &quot;Buy-Sell-Price&quot; for commodity types &quot;Buy&quot; and &quot;Sell&quot;._x000a_" sqref="D1" xr:uid="{BA1F56BD-E1AB-4C7E-A6B6-8E982EDA42C1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum commodity use" prompt="For stock commodities, this value limits annual use (MWh) of this commodity. For CO2, this value limits the amount of emissions (t_CO2). If simulation timespan does not cover a full year, the sums are multiplied accordingly before (cf. 'weight' in urbs)." sqref="E1" xr:uid="{37141B19-04DD-4EF4-8CB3-CF07CB7EAF13}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum commodity use per hour" prompt="For stock commodities, this value limits the energy use per hour (MW)._x000a_" sqref="F1" xr:uid="{AA318DF0-D6F7-424A-B944-C04AAA53323C}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1359,799 +1898,1015 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" style="22" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="24" style="22" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" style="22" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="41" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="13" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" style="42" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.44140625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="35" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="22">
+        <v>0</v>
+      </c>
+      <c r="D2" s="22">
+        <v>56122</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="19">
+        <v>1784013.3448000001</v>
+      </c>
+      <c r="H2" s="36">
+        <v>28544.213516799999</v>
+      </c>
+      <c r="I2" s="37">
+        <v>2.7</v>
+      </c>
+      <c r="J2" s="17">
+        <v>0</v>
+      </c>
+      <c r="K2" s="29">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="L2" s="17">
         <v>40</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>46710</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="M2" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="22">
+        <v>0</v>
+      </c>
+      <c r="D3" s="22">
+        <v>43599</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>2620279.14</v>
-      </c>
-      <c r="H2">
-        <v>9143.1016799999998</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
+      <c r="F3" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="G3" s="28">
+        <v>2230016.6809999999</v>
+      </c>
+      <c r="H3" s="28">
+        <v>43931.328608800002</v>
+      </c>
+      <c r="I3" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="J3" s="17">
+        <v>0</v>
+      </c>
+      <c r="K3" s="29">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="L2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="L3" s="17">
+        <v>40</v>
+      </c>
+      <c r="M3" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>59840</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B4" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0</v>
+      </c>
+      <c r="D4" s="22">
+        <v>999999</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>3345037.2</v>
-      </c>
-      <c r="H3">
-        <v>28432.799999999999</v>
-      </c>
-      <c r="I3">
-        <v>0.35699999999999998</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="F4" s="13">
+        <v>0</v>
+      </c>
+      <c r="G4" s="28">
+        <v>735908.18400000012</v>
+      </c>
+      <c r="H4" s="28">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I4" s="18">
+        <v>2.6</v>
+      </c>
+      <c r="J4" s="19">
+        <v>0</v>
+      </c>
+      <c r="K4" s="29">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="L3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="L4" s="17">
+        <v>25</v>
+      </c>
+      <c r="M4" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="24">
-        <v>999999</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B5" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="22">
+        <v>0</v>
+      </c>
+      <c r="D5" s="22">
+        <v>13483</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F4">
-        <v>0.5</v>
-      </c>
-      <c r="G4">
-        <v>1784013.3448000001</v>
-      </c>
-      <c r="H4">
-        <v>28544.213516799999</v>
-      </c>
-      <c r="I4">
-        <v>2.7</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="L4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="F5" s="13">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>5648000</v>
+      </c>
+      <c r="H5" s="38">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I5">
+        <v>2.6</v>
+      </c>
+      <c r="J5" s="19">
+        <v>0</v>
+      </c>
+      <c r="K5" s="20">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L5" s="17">
+        <v>25</v>
+      </c>
+      <c r="M5" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="24">
-        <v>999999</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="22">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22">
+        <v>14578</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F5">
-        <v>0.65</v>
-      </c>
-      <c r="G5">
-        <v>2230016.6809999999</v>
-      </c>
-      <c r="H5">
-        <v>43931.328608800002</v>
-      </c>
-      <c r="I5">
-        <v>3.2</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="L5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="24">
-        <v>999999</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>0.25</v>
+      <c r="F6" s="13">
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>735908.18400000012</v>
-      </c>
-      <c r="H6">
+        <v>5648000</v>
+      </c>
+      <c r="H6" s="38">
         <v>16725.186000000002</v>
       </c>
       <c r="I6">
         <v>2.6</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="L6">
+      <c r="J6" s="19">
+        <v>0</v>
+      </c>
+      <c r="K6" s="20">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L6" s="17">
         <v>25</v>
       </c>
+      <c r="M6" s="21" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>94200</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="B7" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="22">
+        <v>0</v>
+      </c>
+      <c r="D7" s="22">
+        <v>100000</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>5296308.9000000004</v>
-      </c>
-      <c r="H7">
-        <v>120421.3392</v>
-      </c>
-      <c r="I7">
-        <v>8.5</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="L7">
-        <v>60</v>
+      <c r="F7" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="17">
+        <v>3222374.1032400001</v>
+      </c>
+      <c r="H7" s="17">
+        <v>61882.96289200001</v>
+      </c>
+      <c r="I7" s="18">
+        <v>6.29</v>
+      </c>
+      <c r="J7" s="19">
+        <v>0</v>
+      </c>
+      <c r="K7" s="20">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L7" s="17">
+        <v>40</v>
+      </c>
+      <c r="M7" s="21" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>999999999999</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="B8" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="22">
+        <v>0</v>
+      </c>
+      <c r="D8" s="22">
+        <v>100000</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>5648000</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>53.2</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="L8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="17">
+        <v>3623777.1062800004</v>
+      </c>
+      <c r="H8" s="17">
+        <v>68684.513765600001</v>
+      </c>
+      <c r="I8" s="18">
+        <v>4.7</v>
+      </c>
+      <c r="J8" s="19">
+        <v>0</v>
+      </c>
+      <c r="K8" s="20">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L8" s="17">
+        <v>40</v>
+      </c>
+      <c r="M8" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="23">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15">
-        <v>0</v>
-      </c>
-      <c r="E9" s="16" t="s">
+      <c r="B9" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="22">
+        <v>0</v>
+      </c>
+      <c r="D9" s="22">
+        <v>100000</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="18">
-        <v>3222374.1032400001</v>
-      </c>
-      <c r="H9" s="18">
-        <v>61882.96289200001</v>
-      </c>
-      <c r="I9" s="19">
-        <v>6.29</v>
-      </c>
-      <c r="J9" s="20">
-        <v>0</v>
-      </c>
-      <c r="K9" s="21">
+      <c r="F9" s="13">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1672518.6</v>
+      </c>
+      <c r="H9" s="17">
+        <v>39025.4</v>
+      </c>
+      <c r="I9" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="J9" s="19">
+        <v>0</v>
+      </c>
+      <c r="K9" s="20">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="L9" s="18">
-        <v>40</v>
-      </c>
-      <c r="M9" s="22" t="e">
+      <c r="L9" s="17">
+        <v>25</v>
+      </c>
+      <c r="M9" s="21" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="23">
-        <v>0</v>
-      </c>
-      <c r="D10" s="15">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="22">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22">
+        <v>94198</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="17">
-        <v>0.65</v>
-      </c>
-      <c r="G10" s="18">
-        <v>3623777.1062800004</v>
-      </c>
-      <c r="H10" s="18">
-        <v>68684.513765600001</v>
-      </c>
-      <c r="I10" s="19">
-        <v>4.7</v>
-      </c>
-      <c r="J10" s="20">
-        <v>0</v>
-      </c>
-      <c r="K10" s="21">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="L10" s="18">
-        <v>40</v>
-      </c>
-      <c r="M10" s="22" t="e">
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
+      <c r="G10" s="28">
+        <v>5296308.9000000004</v>
+      </c>
+      <c r="H10" s="36">
+        <v>120421.3392</v>
+      </c>
+      <c r="I10" s="37">
+        <v>8.5</v>
+      </c>
+      <c r="J10" s="17">
+        <v>0</v>
+      </c>
+      <c r="K10" s="29">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="L10" s="17">
+        <v>60</v>
+      </c>
+      <c r="M10" s="21" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="23">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="22">
+        <v>0</v>
+      </c>
+      <c r="D11" s="22">
+        <v>46703</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="17">
-        <v>0.25</v>
-      </c>
-      <c r="G11" s="18">
-        <v>1672518.6</v>
-      </c>
-      <c r="H11" s="18">
-        <v>39025.4</v>
-      </c>
-      <c r="I11" s="19">
-        <v>3.2</v>
-      </c>
-      <c r="J11" s="20">
-        <v>0</v>
-      </c>
-      <c r="K11" s="21">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="L11" s="18">
-        <v>25</v>
-      </c>
-      <c r="M11" s="22" t="e">
+      <c r="F11" s="13">
+        <v>0</v>
+      </c>
+      <c r="G11" s="28">
+        <v>2620279.14</v>
+      </c>
+      <c r="H11" s="28">
+        <v>9143.1016799999998</v>
+      </c>
+      <c r="I11" s="37">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17">
+        <v>0</v>
+      </c>
+      <c r="K11" s="29">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="L11" s="17">
+        <v>60</v>
+      </c>
+      <c r="M11" s="21" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="23">
-        <v>0</v>
-      </c>
-      <c r="D12" s="24">
+      <c r="B12" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="22">
+        <v>0</v>
+      </c>
+      <c r="D12" s="22">
+        <v>61218</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17">
+        <v>3345037.2</v>
+      </c>
+      <c r="H12" s="17">
+        <v>28432.799999999999</v>
+      </c>
+      <c r="I12" s="18">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="J12" s="17">
+        <v>0</v>
+      </c>
+      <c r="K12" s="29">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="L12" s="17">
+        <v>50</v>
+      </c>
+      <c r="M12" s="21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="22">
+        <v>0</v>
+      </c>
+      <c r="D13" s="22">
         <v>999999</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="17">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="30">
-        <v>735908.18400000012</v>
-      </c>
-      <c r="H12" s="30">
-        <v>16725.186000000002</v>
-      </c>
-      <c r="I12" s="19">
-        <v>2.6</v>
-      </c>
-      <c r="J12" s="20">
-        <v>0</v>
-      </c>
-      <c r="K12" s="31">
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="39">
+        <v>5648000</v>
+      </c>
+      <c r="H13" s="39">
+        <v>0</v>
+      </c>
+      <c r="I13" s="40">
+        <v>53.2</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="29">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L13" s="17">
         <v>25</v>
       </c>
-      <c r="M12" s="22" t="e">
+      <c r="M13" s="21" t="e">
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A9:C12">
-    <cfRule type="expression" dxfId="3" priority="1">
+  <conditionalFormatting sqref="P2:XFD4">
+    <cfRule type="expression" dxfId="48" priority="14">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:XFD1 A14:F15 J14:XFD15 A16:XFD1048576 N13:XFD13">
+    <cfRule type="expression" dxfId="47" priority="16">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:XFD12">
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
+    <cfRule type="expression" dxfId="46" priority="15">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:D13 F9:F13 F4:F6">
+    <cfRule type="expression" dxfId="45" priority="13">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4 E12:E13">
+    <cfRule type="expression" dxfId="44" priority="12">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="expression" dxfId="43" priority="11">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="expression" dxfId="42" priority="10">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B9">
+    <cfRule type="expression" dxfId="41" priority="9">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="40" priority="8">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="expression" dxfId="39" priority="7">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" dxfId="38" priority="6">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="37" priority="5">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="36" priority="4">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" dxfId="35" priority="3">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2">
+    <cfRule type="expression" dxfId="34" priority="2">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:I11">
+    <cfRule type="expression" dxfId="33" priority="1">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="11">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Startup Cost (€)" prompt="The process cost which is incurred when the process is switched on from off condition at a timestep." sqref="J1" xr:uid="{441EA231-853B-4653-934D-A4EC373EA3A7}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Weighted average cost of capital" prompt="Percentage (%) of costs for capital after taxes. Used to calculate annuity factor for investment costs." sqref="K1" xr:uid="{A30E3D63-840C-4E32-BFAD-4B570C5365BB}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Area use per capacity (m^2/MW) " prompt="If a process requires area set value here. If no area use is to be considered set NV(). " sqref="M1" xr:uid="{91785600-DE7B-4F7A-AC8F-65C6C851197C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Minimum load fraction" prompt="This value sets the minimum possible fraction of the process capacity which the process can run at." sqref="F1" xr:uid="{9A9ACE0F-A305-418B-95CD-208FD9CA8EE6}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximal power gradient (1/h)" prompt="Maximum allowed power gradient relative to power throughput capacity. Set value to inf or greater than 1/dt to disable it." sqref="E1" xr:uid="{FBBD42A1-E795-4995-9D08-16EF77A9E070}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Depreciation period (a)" prompt="Economic lifetime (more conservative than technical lifetime) of a process investment in years (a). Used to calculate annuity factor for investment costs." sqref="L1" xr:uid="{115F5F6D-72CC-4290-AFA3-30D933871A79}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Variable costs (€/MWh)" prompt="Variable costs per throughput energy unit (MWh) produced. This includes wear and tear of moving parts, operation liquids, but excluding fuel costs, as they are included in table Commodity, column 'price'." sqref="I1" xr:uid="{9F063BAD-D045-49B7-8E35-8AA8A08C302A}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Annual fix cost (€/MW/a)" prompt="Operation independent costs for existing and new capacities per MW throughput power." sqref="H1" xr:uid="{D2C14352-6987-4E80-8F1F-735E6A7C5B11}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Investment cost (€/MW)" prompt="Total investement cost for adding capacity. Is annualized in the model using the annuity factor derived from 'wacc' and 'depreciation'." sqref="G1" xr:uid="{7577BF0E-8C75-415A-ACF6-009CAD795C0D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum capacity (MW)" prompt="Maximum allowed power throughput capacity per process. Must be bigger than or equal to max('cap-lo', 'inst-cap')." sqref="D1" xr:uid="{CBA85EE5-7053-43FA-B664-D5AFB601AA38}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Minimum capacity (MW)" prompt="Minimum required power throughput capacity that is allowed per process. Must be smaller or equal to 'cap-up', but can be bigger than 'inst-cap' to force investment." sqref="C1" xr:uid="{EC04E2AB-3316-49DC-9E7D-09C49386FBF9}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="13" bestFit="1"/>
+    <col min="4" max="4" width="20.6640625" style="44" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" style="44" customWidth="1"/>
+    <col min="6" max="16384" width="11.44140625" style="13"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="D2" s="12">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="27">
+        <v>0.43</v>
+      </c>
+      <c r="E3" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="12">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B5" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="12">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D2">
+      <c r="D6" s="27">
+        <v>0.62</v>
+      </c>
+      <c r="E6" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.125</v>
+      </c>
+      <c r="E7" s="12">
+        <f>D7*E5</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="12">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E8" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0.35</v>
+      </c>
+      <c r="E9" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4">
-        <v>0.36299999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="12">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D5">
+      <c r="D12" s="12">
+        <v>0.38</v>
+      </c>
+      <c r="E12" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="12">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E13" s="12">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="27">
+        <v>0.47</v>
+      </c>
+      <c r="E14" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7">
-        <v>0.125</v>
-      </c>
-      <c r="E7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C15" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D8">
+      <c r="D15" s="12">
+        <v>0.34179999999999999</v>
+      </c>
+      <c r="E15" s="12">
+        <f>D15*E13</f>
+        <v>0.47851999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="12">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="E16" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C17" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D11">
+      <c r="D17" s="12">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="E17" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="12">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="C19" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D13">
+      <c r="D19" s="12">
         <v>1</v>
       </c>
-      <c r="E13">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15">
-        <v>0.34179999999999999</v>
-      </c>
-      <c r="E15">
-        <v>0.47851999999999989</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
+      <c r="E19" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
-        <v>89</v>
+      <c r="A20" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="12">
         <v>1</v>
@@ -2162,35 +2917,35 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
-        <v>89</v>
+      <c r="A21" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="12">
-        <v>0.38</v>
-      </c>
-      <c r="E21" s="12">
-        <f>D21*E19</f>
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E21" s="12" t="e">
+        <f>D21*E18</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>89</v>
+      <c r="A22" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="12">
-        <v>3.4180000000000002E-2</v>
+        <v>3.6299999999999999E-2</v>
       </c>
       <c r="E22" s="12" t="e">
         <f>D22*E20</f>
@@ -2198,68 +2953,67 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>90</v>
+      <c r="A23" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" s="12">
         <v>1</v>
       </c>
-      <c r="E23" s="12" t="e">
+      <c r="E23" s="12">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="12">
+        <v>0.49</v>
+      </c>
+      <c r="E24" s="12" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="12">
-        <v>0.34</v>
-      </c>
-      <c r="E24" s="12">
-        <f>D24*E21</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
-        <v>90</v>
+      <c r="A25" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" s="12">
-        <v>3.6299999999999999E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="E25" s="12" t="e">
-        <f>D25*E23</f>
+        <f>NA()</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="12">
         <v>1</v>
@@ -2270,16 +3024,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="12">
-        <v>0.49</v>
+        <v>50</v>
+      </c>
+      <c r="D27" s="27">
+        <v>0.62</v>
       </c>
       <c r="E27" s="12" t="e">
         <f>NA()</f>
@@ -2288,51 +3042,52 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="12">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="E28" s="12" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
+        <v>50</v>
+      </c>
+      <c r="D28" s="7">
+        <v>0.125</v>
+      </c>
+      <c r="E28" s="12">
+        <f>D28*E26</f>
+        <v>0.15</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
-        <v>94</v>
+      <c r="A29" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="12">
         <v>1</v>
       </c>
-      <c r="E29" s="12">
-        <v>1.2</v>
+      <c r="E29" s="12" t="e">
+        <f>D29*E27</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
-        <v>94</v>
+      <c r="A30" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="29">
-        <v>0.62</v>
+        <v>50</v>
+      </c>
+      <c r="D30" s="12">
+        <v>0.4</v>
       </c>
       <c r="E30" s="12" t="e">
         <f>NA()</f>
@@ -2340,36 +3095,168 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
-        <v>94</v>
+      <c r="A31" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="7">
-        <v>0.125</v>
-      </c>
-      <c r="E31" s="12">
-        <f>D31*E29</f>
-        <v>0.15</v>
+        <v>50</v>
+      </c>
+      <c r="D31" s="12">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E31" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="12">
+        <v>1</v>
+      </c>
+      <c r="E32" s="12" t="e">
+        <f>D32*E30</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="12">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E34" s="12" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A30:C31 E30:E31">
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A20:E25 A26 C26:E26 A27:E29">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+  <conditionalFormatting sqref="A2:C4 E2:XFD19 A30:C31 E30:E31">
+    <cfRule type="expression" dxfId="32" priority="61">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:E29">
+    <cfRule type="expression" dxfId="31" priority="58">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:XFD1 A5 C5 A6:C19">
+    <cfRule type="expression" dxfId="30" priority="73">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:XFD25 A26 C26:XFD26 A27:XFD28 F29:XFD31 A32:XFD33 A35:XFD1048576 F34:XFD34">
+    <cfRule type="expression" dxfId="29" priority="62">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2 D4:D5 D8:D13 D15:D19">
+    <cfRule type="expression" dxfId="28" priority="66">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="dataBar" priority="68">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D5 D8:D13 D15:D19 D2">
+    <cfRule type="dataBar" priority="72">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D10 D5 D2 E2:E7">
+    <cfRule type="dataBar" priority="71">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="dataBar" priority="67">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="dataBar" priority="65">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:D17">
+    <cfRule type="dataBar" priority="70">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:D19">
+    <cfRule type="dataBar" priority="69">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="60">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -2377,20 +3264,29 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F7BA0B4B-90CB-4807-AF4D-1EDF02AFA3FD}</x14:id>
+          <x14:id>{2A8C49CC-DA0D-4191-BBFB-5FE50C459800}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D1:E1">
+    <cfRule type="dataBar" priority="79">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D20:E28">
-    <cfRule type="dataBar" priority="7">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="8">
+    <cfRule type="dataBar" priority="63">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="64">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -2399,7 +3295,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29 E30:E31">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="59">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -2407,17 +3303,554 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F299514B-B7B7-43FD-A307-67B6928AA493}</x14:id>
+          <x14:id>{FB16898D-49AA-405C-859E-C20A59E0D6F2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D32:E33 D35:E1048576">
+    <cfRule type="dataBar" priority="80">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E10">
+    <cfRule type="dataBar" priority="77">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E12">
+    <cfRule type="dataBar" priority="78">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="dataBar" priority="76">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:E17">
+    <cfRule type="dataBar" priority="75">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18:E19">
+    <cfRule type="dataBar" priority="74">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34:E34">
+    <cfRule type="expression" dxfId="27" priority="56">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34:E34">
+    <cfRule type="dataBar" priority="57">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:E1">
+    <cfRule type="expression" dxfId="26" priority="54">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:C25 A27:C28 A32:E32">
+    <cfRule type="expression" dxfId="25" priority="53">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:E1">
+    <cfRule type="dataBar" priority="55">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5 A6:C19 D8:E12 B2:C4 D16:E19">
+    <cfRule type="expression" dxfId="24" priority="47">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:C25 C26 B27:C27">
+    <cfRule type="expression" dxfId="23" priority="44">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:C20 A26:A28">
+    <cfRule type="expression" dxfId="22" priority="45">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" dxfId="21" priority="42">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="dataBar" priority="51">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{42FA673F-28A5-4481-89A4-FDA06EBCCB49}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D12 D16:D19">
+    <cfRule type="dataBar" priority="46">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9EDAE71E-28CA-4AC8-B137-63FC0BC16B84}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:E12">
+    <cfRule type="dataBar" priority="52">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1844411D-0F8A-45B0-BA16-09EF5C8E7CEC}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:E17">
+    <cfRule type="dataBar" priority="49">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B18AF491-BBCE-4E3E-ABD5-943264E2CC37}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:E19">
+    <cfRule type="dataBar" priority="48">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{CE34E259-5234-4648-8590-2E9A2D42BBE1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E10">
+    <cfRule type="dataBar" priority="50">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A20AA5C9-A4DE-4DD5-85A8-35BAB47E2403}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:E34">
+    <cfRule type="expression" dxfId="20" priority="41">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:C28">
+    <cfRule type="expression" dxfId="19" priority="43">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="18" priority="40">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:A31">
+    <cfRule type="expression" dxfId="17" priority="39">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:A34">
+    <cfRule type="expression" dxfId="16" priority="38">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29 B30:C30">
+    <cfRule type="expression" dxfId="15" priority="36">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="dataBar" priority="35">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A74363D2-9B8A-4D51-9519-C71DAEEDFDFA}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30">
+    <cfRule type="dataBar" priority="37">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D9CD184D-2ACA-4929-A397-BA85A74FFD19}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31">
+    <cfRule type="dataBar" priority="34">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D6B172E0-C1DD-4B30-8E5E-2CFAC14CCBB1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:C31">
+    <cfRule type="expression" dxfId="14" priority="33">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32 B33:C33">
+    <cfRule type="expression" dxfId="13" priority="31">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32">
+    <cfRule type="dataBar" priority="30">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9E96561D-595A-4DA4-886F-54F30B6E2A28}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33">
+    <cfRule type="dataBar" priority="32">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4C5C2378-96DC-4A19-8A4D-600A5FB7F76D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34">
+    <cfRule type="dataBar" priority="29">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9C68EAFF-AB58-4369-BEB0-72F00815FAC9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:C34">
+    <cfRule type="expression" dxfId="12" priority="28">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A22">
+    <cfRule type="expression" dxfId="11" priority="27">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="expression" dxfId="10" priority="26">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="expression" dxfId="9" priority="24">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D79336F9-F609-4AE8-83E3-1D21BA56B453}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="dataBar" priority="25">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1B6DE447-9E25-47A7-B260-EC0E83910F29}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27:E28">
+    <cfRule type="expression" dxfId="8" priority="19">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26:E26">
+    <cfRule type="expression" dxfId="7" priority="16">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E25">
+    <cfRule type="expression" dxfId="6" priority="20">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26">
+    <cfRule type="dataBar" priority="18">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F62C9548-0325-4EFA-9498-92191B19DF09}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E25">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26:E26 E27:E28">
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{70495254-74D8-429A-AF67-939B2403A33E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4">
+    <cfRule type="expression" dxfId="5" priority="11">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2 D4">
+    <cfRule type="expression" dxfId="4" priority="12">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4 D2">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4 D2">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E7">
+    <cfRule type="expression" dxfId="3" priority="7">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" dxfId="2" priority="8">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E7 D5">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Ratio (1)" prompt="Input/output quantities, relative to process throughput" sqref="D1" xr:uid="{8CDF577A-1E49-4537-B2ED-FE655E5663EB}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Ratio at minimum operation point" prompt="Input/Output ratio at point of minimum operation (min-fract in 'Process' sheet)._x000a__x000a_All values have to be larger/equal to ratio!" sqref="E1" xr:uid="{4C956E3A-AA12-404F-BC48-BD2852B10DAE}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F7BA0B4B-90CB-4807-AF4D-1EDF02AFA3FD}">
+          <x14:cfRule type="dataBar" id="{2A8C49CC-DA0D-4191-BBFB-5FE50C459800}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -2432,7 +3865,7 @@
           <xm:sqref>D29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F299514B-B7B7-43FD-A307-67B6928AA493}">
+          <x14:cfRule type="dataBar" id="{FB16898D-49AA-405C-859E-C20A59E0D6F2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -2445,6 +3878,246 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>D29:E29 E30:E31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{42FA673F-28A5-4481-89A4-FDA06EBCCB49}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D8:D10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9EDAE71E-28CA-4AC8-B137-63FC0BC16B84}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D8:D12 D16:D19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1844411D-0F8A-45B0-BA16-09EF5C8E7CEC}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D11:E12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B18AF491-BBCE-4E3E-ABD5-943264E2CC37}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D16:E17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{CE34E259-5234-4648-8590-2E9A2D42BBE1}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D18:E19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A20AA5C9-A4DE-4DD5-85A8-35BAB47E2403}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E8:E10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A74363D2-9B8A-4D51-9519-C71DAEEDFDFA}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D9CD184D-2ACA-4929-A397-BA85A74FFD19}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E30</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D6B172E0-C1DD-4B30-8E5E-2CFAC14CCBB1}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9E96561D-595A-4DA4-886F-54F30B6E2A28}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4C5C2378-96DC-4A19-8A4D-600A5FB7F76D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9C68EAFF-AB58-4369-BEB0-72F00815FAC9}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D79336F9-F609-4AE8-83E3-1D21BA56B453}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:D34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1B6DE447-9E25-47A7-B260-EC0E83910F29}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:D34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F62C9548-0325-4EFA-9498-92191B19DF09}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{70495254-74D8-429A-AF67-939B2403A33E}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D26:E26 E27:E28</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2459,19 +4132,19 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>33</v>
@@ -2495,13 +4168,13 @@
         <v>38</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2519,46 +4192,46 @@
         <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>37</v>
@@ -2567,13 +4240,13 @@
         <v>38</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2581,7 +4254,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2640,7 +4313,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2699,7 +4372,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2771,19 +4444,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2801,10 +4474,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
